--- a/outputs/D_skew_5deg.xlsx
+++ b/outputs/D_skew_5deg.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$313</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$2</definedName>
@@ -2371,7 +2371,7 @@
         <v>0.96</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>3.573</v>
+        <v>5.008</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>0.96</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>3.729</v>
+        <v>5.022</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3040,95 +3040,131 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>9.15</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
+        <v>11.689</v>
+      </c>
+    </row>
+    <row r="4" ht="119" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Yellow cells</t>
+          <t>Text encoding</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Review required. See Validation Report for the reason and source row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
+          <t>All XLSX string fields use a reversible encoding: a literal backslash is doubled; XML-forbidden code points use a backslash followed by u and four hexadecimal digits. An underscore starting an OOXML escape-like sequence uses the same Unicode encoding. Decode left to right, treating each doubled backslash as one literal backslash. The full audit JSON and saved workspace retain the original strings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="68" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Source row</t>
+          <t>Long text</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Data row within the extracted source table, excluding detected headers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
+          <t>Values exceeding Excel's 32767-character cell limit show an explicit preview. The Long Text sheet preserves the complete encoded value in numbered chunks. Join its chunks in order before decoding the text encoding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="68" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Confidence</t>
+          <t>Small numbers</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Extraction heuristic / OCR score, not a calibrated probability of correctness.</t>
+          <t>Numbers below Excel's normal floating-point range remain exact text. Numbers needing more than 12 decimal places use General formatting; percentages needing more than 12 display decimals remain text, avoiding a false zero.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Dates</t>
+          <t>Yellow cells</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>ISO and unambiguous day-first dates are typed. Ambiguous dates stay text.</t>
+          <t>Review required. See Validation Report for the reason and source row.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Source row</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Source strings are stored as text. No source formulas are executed.</t>
+          <t>Data row within the extracted source table, excluding detected headers.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Cell evidence</t>
+          <t>Confidence</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Ctrl+click a linked data cell for its source bounding box and original readings.</t>
+          <t>Extraction heuristic / OCR score, not a calibrated probability of correctness.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>ISO and unambiguous day-first dates are typed. Ambiguous dates stay text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Source strings are stored as text. No source formulas are executed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Cell evidence</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Ctrl+click a linked data cell for its source bounding box and original readings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>Repair proposals</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Arithmetic-derived suggestions only. Source documents may contain errors. Never applied automatically.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10"/>
+  <autoFilter ref="A1:B13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3240,16 +3276,16 @@
         <v>1</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>8.43</v>
+        <v>8.284000000000001</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>136.478</v>
+        <v>134.804</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>95.095</v>
+        <v>95.262</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>167.068</v>
+        <v>168.981</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -3287,16 +3323,16 @@
         <v>2</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>8.43</v>
+        <v>8.284000000000001</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>136.478</v>
+        <v>134.804</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>95.095</v>
+        <v>95.262</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>167.068</v>
+        <v>168.981</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -3334,16 +3370,16 @@
         <v>1</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>93.06699999999999</v>
+        <v>92.92100000000001</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>128.619</v>
+        <v>126.945</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>184.992</v>
+        <v>185.159</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>159.669</v>
+        <v>161.582</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -3381,16 +3417,16 @@
         <v>2</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>93.06699999999999</v>
+        <v>92.92100000000001</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>128.619</v>
+        <v>126.945</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>184.992</v>
+        <v>185.159</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>159.669</v>
+        <v>161.582</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -3428,16 +3464,16 @@
         <v>1</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>182.964</v>
+        <v>182.818</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>120.802</v>
+        <v>119.128</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>274.411</v>
+        <v>274.578</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>151.811</v>
+        <v>153.723</v>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
@@ -3475,16 +3511,16 @@
         <v>2</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>182.964</v>
+        <v>182.818</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>120.802</v>
+        <v>119.128</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>274.411</v>
+        <v>274.578</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>151.811</v>
+        <v>153.723</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
@@ -3522,16 +3558,16 @@
         <v>1</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>272.383</v>
+        <v>272.237</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>114.26</v>
+        <v>112.586</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>349.245</v>
+        <v>349.413</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>143.994</v>
+        <v>145.906</v>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
@@ -3569,16 +3605,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>272.383</v>
+        <v>272.237</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>114.26</v>
+        <v>112.586</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>349.245</v>
+        <v>349.413</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>143.994</v>
+        <v>145.906</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
@@ -3616,16 +3652,16 @@
         <v>1</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>347.218</v>
+        <v>347.072</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>98.584</v>
+        <v>96.911</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>528.561</v>
+        <v>528.729</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>137.452</v>
+        <v>139.364</v>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
@@ -3663,16 +3699,16 @@
         <v>2</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>347.218</v>
+        <v>347.072</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>98.584</v>
+        <v>96.911</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>528.561</v>
+        <v>528.729</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>137.452</v>
+        <v>139.364</v>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
@@ -3710,16 +3746,16 @@
         <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>526.534</v>
+        <v>526.388</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>93.798</v>
+        <v>92.124</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>583.313</v>
+        <v>583.48</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>121.776</v>
+        <v>123.688</v>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
@@ -3757,16 +3793,16 @@
         <v>2</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>526.534</v>
+        <v>526.388</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>93.798</v>
+        <v>92.124</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>583.313</v>
+        <v>583.48</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>121.776</v>
+        <v>123.688</v>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
@@ -3804,16 +3840,16 @@
         <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>581.285</v>
+        <v>581.139</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>87.69499999999999</v>
+        <v>86.021</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>653.126</v>
+        <v>653.294</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>116.989</v>
+        <v>118.902</v>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
@@ -3851,16 +3887,16 @@
         <v>2</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>581.285</v>
+        <v>581.139</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>87.69499999999999</v>
+        <v>86.021</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>653.126</v>
+        <v>653.294</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>116.989</v>
+        <v>118.902</v>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
@@ -3898,16 +3934,16 @@
         <v>1</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>651.099</v>
+        <v>650.953</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>80.714</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>732.982</v>
+        <v>733.149</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>110.886</v>
+        <v>112.799</v>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
@@ -3945,16 +3981,16 @@
         <v>2</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>651.099</v>
+        <v>650.953</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>80.714</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>732.982</v>
+        <v>733.149</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>110.886</v>
+        <v>112.799</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
@@ -3992,16 +4028,16 @@
         <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>730.954</v>
+        <v>730.808</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>74.611</v>
+        <v>72.937</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>802.796</v>
+        <v>802.963</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>103.905</v>
+        <v>105.818</v>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
@@ -4039,16 +4075,16 @@
         <v>2</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>730.954</v>
+        <v>730.808</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>74.611</v>
+        <v>72.937</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>802.796</v>
+        <v>802.963</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>103.905</v>
+        <v>105.818</v>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
@@ -4086,16 +4122,16 @@
         <v>1</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>800.768</v>
+        <v>800.622</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>68.967</v>
+        <v>67.294</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>867.349</v>
+        <v>867.5170000000001</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>97.80200000000001</v>
+        <v>99.715</v>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
@@ -4133,16 +4169,16 @@
         <v>2</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>800.768</v>
+        <v>800.622</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>68.967</v>
+        <v>67.294</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>867.349</v>
+        <v>867.5170000000001</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>97.80200000000001</v>
+        <v>99.715</v>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
@@ -4180,16 +4216,16 @@
         <v>1</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>865.322</v>
+        <v>865.176</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>61.129</v>
+        <v>59.456</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>957.0069999999999</v>
+        <v>957.175</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>92.15900000000001</v>
+        <v>94.072</v>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
@@ -4227,16 +4263,16 @@
         <v>2</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>865.322</v>
+        <v>865.176</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>61.129</v>
+        <v>59.456</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>957.0069999999999</v>
+        <v>957.175</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>92.15900000000001</v>
+        <v>94.072</v>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
@@ -4274,16 +4310,16 @@
         <v>1</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>954.98</v>
+        <v>954.8339999999999</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>52.414</v>
+        <v>50.74</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>1056.707</v>
+        <v>1056.874</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>84.321</v>
+        <v>86.23399999999999</v>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
@@ -4321,16 +4357,16 @@
         <v>2</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>954.98</v>
+        <v>954.8339999999999</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>52.414</v>
+        <v>50.74</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>1056.707</v>
+        <v>1056.874</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>84.321</v>
+        <v>86.23399999999999</v>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
@@ -4368,10 +4404,10 @@
         <v>1</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>10.457</v>
+        <v>10.625</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>159.669</v>
+        <v>161.582</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>97.60299999999999</v>
@@ -4419,10 +4455,10 @@
         <v>1</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>95.095</v>
+        <v>95.262</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>151.811</v>
+        <v>153.723</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>187.5</v>
@@ -4470,10 +4506,10 @@
         <v>1</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>184.992</v>
+        <v>185.159</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>143.994</v>
+        <v>145.906</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>276.919</v>
@@ -4521,10 +4557,10 @@
         <v>1</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>274.411</v>
+        <v>274.578</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>137.452</v>
+        <v>139.364</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>351.754</v>
@@ -4572,10 +4608,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>349.245</v>
+        <v>349.413</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>121.776</v>
+        <v>123.688</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>531.0700000000001</v>
@@ -4623,10 +4659,10 @@
         <v>1</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>528.561</v>
+        <v>528.729</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>116.989</v>
+        <v>118.902</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>585.821</v>
@@ -4674,10 +4710,10 @@
         <v>1</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>583.313</v>
+        <v>583.48</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>110.886</v>
+        <v>112.799</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>655.635</v>
@@ -4725,10 +4761,10 @@
         <v>1</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>653.126</v>
+        <v>653.294</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>103.905</v>
+        <v>105.818</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>735.49</v>
@@ -4776,10 +4812,10 @@
         <v>1</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>732.982</v>
+        <v>733.149</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>97.80200000000001</v>
+        <v>99.715</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>805.304</v>
@@ -4827,10 +4863,10 @@
         <v>1</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>802.796</v>
+        <v>802.963</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>92.15900000000001</v>
+        <v>94.072</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>869.8579999999999</v>
@@ -4878,10 +4914,10 @@
         <v>1</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>867.349</v>
+        <v>867.5170000000001</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>84.321</v>
+        <v>86.23399999999999</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>959.516</v>
@@ -4929,10 +4965,10 @@
         <v>1</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>957.0069999999999</v>
+        <v>957.175</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>75.605</v>
+        <v>77.518</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1059.215</v>
@@ -11712,10 +11748,10 @@
         <v>2</v>
       </c>
       <c r="E170" s="7" t="n">
-        <v>10.457</v>
+        <v>10.625</v>
       </c>
       <c r="F170" s="7" t="n">
-        <v>159.669</v>
+        <v>161.582</v>
       </c>
       <c r="G170" s="7" t="n">
         <v>97.60299999999999</v>
@@ -11763,10 +11799,10 @@
         <v>2</v>
       </c>
       <c r="E171" s="7" t="n">
-        <v>95.095</v>
+        <v>95.262</v>
       </c>
       <c r="F171" s="7" t="n">
-        <v>151.811</v>
+        <v>153.723</v>
       </c>
       <c r="G171" s="7" t="n">
         <v>187.5</v>
@@ -11814,10 +11850,10 @@
         <v>2</v>
       </c>
       <c r="E172" s="7" t="n">
-        <v>184.992</v>
+        <v>185.159</v>
       </c>
       <c r="F172" s="7" t="n">
-        <v>143.994</v>
+        <v>145.906</v>
       </c>
       <c r="G172" s="7" t="n">
         <v>276.919</v>
@@ -11865,10 +11901,10 @@
         <v>2</v>
       </c>
       <c r="E173" s="7" t="n">
-        <v>274.411</v>
+        <v>274.578</v>
       </c>
       <c r="F173" s="7" t="n">
-        <v>137.452</v>
+        <v>139.364</v>
       </c>
       <c r="G173" s="7" t="n">
         <v>351.754</v>
@@ -11916,10 +11952,10 @@
         <v>2</v>
       </c>
       <c r="E174" s="7" t="n">
-        <v>349.245</v>
+        <v>349.413</v>
       </c>
       <c r="F174" s="7" t="n">
-        <v>121.776</v>
+        <v>123.688</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>531.0700000000001</v>
@@ -11967,10 +12003,10 @@
         <v>2</v>
       </c>
       <c r="E175" s="7" t="n">
-        <v>528.561</v>
+        <v>528.729</v>
       </c>
       <c r="F175" s="7" t="n">
-        <v>116.989</v>
+        <v>118.902</v>
       </c>
       <c r="G175" s="7" t="n">
         <v>585.821</v>
@@ -12018,10 +12054,10 @@
         <v>2</v>
       </c>
       <c r="E176" s="7" t="n">
-        <v>583.313</v>
+        <v>583.48</v>
       </c>
       <c r="F176" s="7" t="n">
-        <v>110.886</v>
+        <v>112.799</v>
       </c>
       <c r="G176" s="7" t="n">
         <v>655.635</v>
@@ -12069,10 +12105,10 @@
         <v>2</v>
       </c>
       <c r="E177" s="7" t="n">
-        <v>653.126</v>
+        <v>653.294</v>
       </c>
       <c r="F177" s="7" t="n">
-        <v>103.905</v>
+        <v>105.818</v>
       </c>
       <c r="G177" s="7" t="n">
         <v>735.49</v>
@@ -12120,10 +12156,10 @@
         <v>2</v>
       </c>
       <c r="E178" s="7" t="n">
-        <v>732.982</v>
+        <v>733.149</v>
       </c>
       <c r="F178" s="7" t="n">
-        <v>97.80200000000001</v>
+        <v>99.715</v>
       </c>
       <c r="G178" s="7" t="n">
         <v>805.304</v>
@@ -12171,10 +12207,10 @@
         <v>2</v>
       </c>
       <c r="E179" s="7" t="n">
-        <v>802.796</v>
+        <v>802.963</v>
       </c>
       <c r="F179" s="7" t="n">
-        <v>92.15900000000001</v>
+        <v>94.072</v>
       </c>
       <c r="G179" s="7" t="n">
         <v>869.8579999999999</v>
@@ -12222,10 +12258,10 @@
         <v>2</v>
       </c>
       <c r="E180" s="7" t="n">
-        <v>867.349</v>
+        <v>867.5170000000001</v>
       </c>
       <c r="F180" s="7" t="n">
-        <v>84.321</v>
+        <v>86.23399999999999</v>
       </c>
       <c r="G180" s="7" t="n">
         <v>959.516</v>
@@ -12273,10 +12309,10 @@
         <v>2</v>
       </c>
       <c r="E181" s="7" t="n">
-        <v>957.0069999999999</v>
+        <v>957.175</v>
       </c>
       <c r="F181" s="7" t="n">
-        <v>75.605</v>
+        <v>77.518</v>
       </c>
       <c r="G181" s="7" t="n">
         <v>1059.215</v>
@@ -19091,7 +19127,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>18058a4a270042cb8b1ce1d3ad7d7ecc8f8dd0c6144b8f1cbafacf56406e9a18</t>
+          <t>c90805221ed4c1f28bb6943bb2c8f61e2c47369af7f6c68bbee8939eb19cb9aa</t>
         </is>
       </c>
     </row>

--- a/outputs/D_skew_5deg.xlsx
+++ b/outputs/D_skew_5deg.xlsx
@@ -10,25 +10,27 @@
     <sheet name="Data 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Validation Report" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Page Audit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Read me" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cell Evidence" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Verification" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Constraints" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Repair Proposals" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Correction History" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Join Receipt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Read me" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cell Evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Verification" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Constraints" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Repair Proposals" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Correction History" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data 1'!$A$1:$L$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$313</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Correction History'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Join Receipt'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Provenance'!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$M$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2082,6 +2084,79 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Excel row</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Supporting equations</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
@@ -2371,7 +2446,7 @@
         <v>0.96</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>5.008</v>
+        <v>7.404</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -2413,7 +2488,7 @@
         <v>0.96</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>5.022</v>
+        <v>7.463</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
@@ -2444,6 +2519,133 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Source pages</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Page joins</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Repeated headers removed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Split rows recovered</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PDF page</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source rows on page</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Output rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2996,7 +3198,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3040,7 +3242,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>11.689</v>
+        <v>18.599</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -3169,7 +3371,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19082,7 +19284,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19127,7 +19329,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>c90805221ed4c1f28bb6943bb2c8f61e2c47369af7f6c68bbee8939eb19cb9aa</t>
+          <t>7c0a6ab7d42dc988ea3343f691c82e7e034c1b727b004b4dd14ef16d1f8fb22d</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19431,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19326,77 +19528,4 @@
   <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Excel row</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Supporting equations</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>